--- a/monthly_closing_template.xlsx
+++ b/monthly_closing_template.xlsx
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="B11" s="171">
-        <f>'매출액대비 비율분석'!C41</f>
+        <f>'매출액대비 비율분석'!C42</f>
         <v/>
       </c>
       <c r="C11" s="172">
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
       <c r="F11" s="171">
-        <f>'매출액대비 비율분석'!F41</f>
+        <f>'매출액대비 비율분석'!F42</f>
         <v/>
       </c>
       <c r="G11" s="172">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B12" s="168">
-        <f>'매출액대비 비율분석'!C42</f>
+        <f>'매출액대비 비율분석'!C43</f>
         <v/>
       </c>
       <c r="C12" s="169">
@@ -3153,7 +3153,7 @@
         <v/>
       </c>
       <c r="F12" s="168">
-        <f>'매출액대비 비율분석'!F42</f>
+        <f>'매출액대비 비율분석'!F43</f>
         <v/>
       </c>
       <c r="G12" s="169">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="B13" s="168">
-        <f>'매출액대비 비율분석'!C50</f>
+        <f>'매출액대비 비율분석'!C51</f>
         <v/>
       </c>
       <c r="C13" s="169">
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="F13" s="168">
-        <f>'매출액대비 비율분석'!F50</f>
+        <f>'매출액대비 비율분석'!F51</f>
         <v/>
       </c>
       <c r="G13" s="169">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="B14" s="171">
-        <f>'매출액대비 비율분석'!C58</f>
+        <f>'매출액대비 비율분석'!C59</f>
         <v/>
       </c>
       <c r="C14" s="172">
@@ -3223,7 +3223,7 @@
         <v/>
       </c>
       <c r="F14" s="171">
-        <f>'매출액대비 비율분석'!F58</f>
+        <f>'매출액대비 비율분석'!F59</f>
         <v/>
       </c>
       <c r="G14" s="172">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="B15" s="168">
-        <f>'매출액대비 비율분석'!C59</f>
+        <f>'매출액대비 비율분석'!C60</f>
         <v/>
       </c>
       <c r="C15" s="169">
@@ -3258,7 +3258,7 @@
         <v/>
       </c>
       <c r="F15" s="168">
-        <f>'매출액대비 비율분석'!F59</f>
+        <f>'매출액대비 비율분석'!F60</f>
         <v/>
       </c>
       <c r="G15" s="169">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="B16" s="171">
-        <f>'매출액대비 비율분석'!C61</f>
+        <f>'매출액대비 비율분석'!C62</f>
         <v/>
       </c>
       <c r="C16" s="172">
@@ -3293,7 +3293,7 @@
         <v/>
       </c>
       <c r="F16" s="171">
-        <f>'매출액대비 비율분석'!F61</f>
+        <f>'매출액대비 비율분석'!F62</f>
         <v/>
       </c>
       <c r="G16" s="172">
